--- a/data/village_names_review.xlsx
+++ b/data/village_names_review.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review'!$A$1:$R$430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review'!$A$1:$V$430</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R430"/>
+  <dimension ref="A1:V430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -557,6 +557,10 @@
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -650,6 +654,26 @@
           <t>Reviewer note</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>gazetteer_devanagari</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>advisory_body_form</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>gazetteer_page</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>luis_spelling</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -670,7 +694,6 @@
           <t>Agonda</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>DEVALKAJJAN</t>
@@ -726,7 +749,6 @@
           <t>Angediva</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>CHAURI</t>
@@ -772,7 +794,6 @@
           <t>Canacona</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -808,7 +829,6 @@
           <t>Chaudi</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -844,7 +864,6 @@
           <t>Cola</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>KOLA</t>
@@ -895,7 +914,6 @@
           <t>Cotigao</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>COTIGAO</t>
@@ -941,7 +959,6 @@
           <t>Gaodongrem</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>GAUNDONGREN</t>
@@ -987,7 +1004,6 @@
           <t>Loliem</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>LOLEN</t>
@@ -1038,7 +1054,6 @@
           <t>Nagorcem - Palolem</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -1074,7 +1089,6 @@
           <t>Poinguinim</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>POINGUNIN</t>
@@ -1120,7 +1134,6 @@
           <t>Aglote</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>AALOT</t>
@@ -1171,7 +1184,6 @@
           <t>Bandoli</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>BANDOLI</t>
@@ -1217,7 +1229,6 @@
           <t>Camarconda</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>KAMARKHAND</t>
@@ -1263,7 +1274,6 @@
           <t>Caranzol</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>KARANJHOL</t>
@@ -1309,7 +1319,6 @@
           <t>Codli</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>KODLI</t>
@@ -1355,7 +1364,6 @@
           <t>Colem</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>KOLEM</t>
@@ -1381,6 +1389,11 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="n"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Kulem</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1401,7 +1414,6 @@
           <t>Cormonem</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -1437,7 +1449,6 @@
           <t>Darbandora</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>DARBANDORA</t>
@@ -1483,7 +1494,6 @@
           <t>Moissal</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>KAMARKHAND</t>
@@ -1529,7 +1539,6 @@
           <t>Molem</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>MOLEN</t>
@@ -1575,7 +1584,6 @@
           <t>Piliem</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -1611,7 +1619,6 @@
           <t>Sancordem</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>SAKVORDE</t>
@@ -1657,7 +1664,6 @@
           <t>Sangod</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>SANGOD</t>
@@ -1703,7 +1709,6 @@
           <t>Sigao</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>SHIGAON</t>
@@ -1749,7 +1754,6 @@
           <t>Sonauli</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>SONAULI</t>
@@ -1795,7 +1799,6 @@
           <t>Surla</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>SURLA</t>
@@ -1841,7 +1844,6 @@
           <t>Adnem</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>ADNE</t>
@@ -1892,7 +1894,6 @@
           <t>Ambaulim</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>AMBAVALI</t>
@@ -1943,7 +1944,6 @@
           <t>Amona</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -1979,7 +1979,6 @@
           <t>Assolda</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>ASOLDA</t>
@@ -2030,7 +2029,6 @@
           <t>Avedem</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>AVEDEN</t>
@@ -2081,7 +2079,6 @@
           <t>Bali</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>BALLY</t>
@@ -2132,7 +2129,6 @@
           <t>Barcem</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>BARSEN</t>
@@ -2183,7 +2179,6 @@
           <t>Bendordem</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>BENDODE</t>
@@ -2234,7 +2229,6 @@
           <t>Cacora</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2270,7 +2264,6 @@
           <t>Cavorem</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2306,7 +2299,6 @@
           <t>Cazur</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>BAMBUBOUTHAN</t>
@@ -2352,7 +2344,6 @@
           <t>Chaifi</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>CHAYAPHI</t>
@@ -2398,7 +2389,6 @@
           <t>Cordem</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2434,7 +2424,6 @@
           <t>Corla</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>KARL  KAJUGATTO</t>
@@ -2480,7 +2469,6 @@
           <t>Cotombi</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>KAKODA</t>
@@ -2526,7 +2514,6 @@
           <t>Curchorem</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2562,7 +2549,6 @@
           <t>Cusmane</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2598,7 +2584,6 @@
           <t>Deao</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2634,7 +2619,6 @@
           <t>Fatorpa</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>FATARPA</t>
@@ -2685,7 +2669,6 @@
           <t>Goculdem</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>GOKOLE</t>
@@ -2736,7 +2719,6 @@
           <t>Hodar</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -2772,7 +2754,6 @@
           <t>Maina</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>MAYNA</t>
@@ -2823,7 +2804,6 @@
           <t>Mangal</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>MANGAL</t>
@@ -2869,7 +2849,6 @@
           <t>Molcopona</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>MALKAPOM</t>
@@ -2915,7 +2894,6 @@
           <t>Molcornem</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>MALKARNE</t>
@@ -2966,7 +2944,6 @@
           <t>Morpirla</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -3002,7 +2979,6 @@
           <t>Nagvem</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>NAGVEM</t>
@@ -3048,7 +3024,6 @@
           <t>Naqueri</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>NAKERI</t>
@@ -3099,7 +3074,6 @@
           <t>Padi</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>PADI</t>
@@ -3150,7 +3124,6 @@
           <t>Pirla</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>PIRL</t>
@@ -3201,7 +3174,6 @@
           <t>Quedem</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>KHEDE</t>
@@ -3252,7 +3224,6 @@
           <t>Quepem</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -3288,7 +3259,6 @@
           <t>Quisconda</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>KISKON</t>
@@ -3334,7 +3304,6 @@
           <t>Quitol</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>KITAL</t>
@@ -3380,7 +3349,6 @@
           <t>Sirvoi</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>SHIRVAI</t>
@@ -3431,7 +3399,6 @@
           <t>Sulcorna</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>SURKARN</t>
@@ -3477,7 +3444,6 @@
           <t>Tiloi</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -3513,7 +3479,6 @@
           <t>Undorna</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>UDANA</t>
@@ -3619,7 +3584,6 @@
           <t>Xelvona</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -3655,7 +3619,6 @@
           <t>Xic-Xelvona</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>SHIKSHELVAN</t>
@@ -3706,7 +3669,6 @@
           <t>Zanodem</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>ZANODA</t>
@@ -3757,7 +3719,6 @@
           <t>Antoriem</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>ANTORIEM</t>
@@ -3803,7 +3764,6 @@
           <t>Bati</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>BATI</t>
@@ -3854,7 +3814,6 @@
           <t>Boma</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>BOMA</t>
@@ -3900,7 +3859,6 @@
           <t>Calem</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>COLEM</t>
@@ -3946,7 +3904,6 @@
           <t>Colomb</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>KOLAMBA</t>
@@ -3997,7 +3954,6 @@
           <t>Comproi</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>KANPRAY</t>
@@ -4043,7 +3999,6 @@
           <t>Coranginim</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>KORANGUINIM</t>
@@ -4089,7 +4044,6 @@
           <t>Costi</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>KASHTI</t>
@@ -4140,7 +4094,6 @@
           <t>Cotarli</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>KOTARLI</t>
@@ -4186,7 +4139,6 @@
           <t>Cumbari</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>KUMBARI</t>
@@ -4232,7 +4184,6 @@
           <t>Curdem</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>KURDI</t>
@@ -4288,7 +4239,6 @@
           <t>Dongor</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>DONGAR</t>
@@ -4334,7 +4284,6 @@
           <t>Dongurli</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>DONGURLI</t>
@@ -4380,7 +4329,6 @@
           <t>Dudal</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>DUDAL</t>
@@ -4431,7 +4379,6 @@
           <t>Kurpem</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>KURPE</t>
@@ -4482,7 +4429,6 @@
           <t>Maulinguem</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>MALINGEM</t>
@@ -4528,7 +4474,6 @@
           <t>Muguli</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>MUGULI</t>
@@ -4579,7 +4524,6 @@
           <t>Naiquinim</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>NAIQUINIM</t>
@@ -4625,7 +4569,6 @@
           <t>Neturlim</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>NETRAVLI</t>
@@ -4676,7 +4619,6 @@
           <t>Nundem</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>NUNE</t>
@@ -4722,7 +4664,6 @@
           <t>Odxel</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>OXEL</t>
@@ -4768,7 +4709,6 @@
           <t>Patiem</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>PATIEM</t>
@@ -4814,7 +4754,6 @@
           <t>Porteem</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>PORTEM</t>
@@ -4860,7 +4799,6 @@
           <t>Potrem</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>POTREM</t>
@@ -4906,7 +4844,6 @@
           <t>Rivona</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>REVONA</t>
@@ -4962,7 +4899,6 @@
           <t>Rumbrem</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>RUMBREM</t>
@@ -5013,7 +4949,6 @@
           <t>Salauli</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>SALAVLI</t>
@@ -5059,7 +4994,6 @@
           <t>Sanguem</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -5095,7 +5029,6 @@
           <t>Santona</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>SANTONA</t>
@@ -5196,7 +5129,6 @@
           <t>Sigonem</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>SIGONEM</t>
@@ -5247,7 +5179,6 @@
           <t>Todou</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>TODOV</t>
@@ -5293,7 +5224,6 @@
           <t>Uguem</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>UGEM</t>
@@ -5344,7 +5274,6 @@
           <t>Verlem</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>VERLEN</t>
@@ -5395,7 +5324,6 @@
           <t>Vichundrem</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>DIGALI</t>
@@ -5446,7 +5374,6 @@
           <t>Viliena</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>VILYAN</t>
@@ -5492,7 +5419,6 @@
           <t>Xelpem</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>SHELPE</t>
@@ -5588,6 +5514,11 @@
       <c r="P107" s="2" t="n"/>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Oidone</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5643,6 +5574,11 @@
       <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="n"/>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Honjunnem</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5663,7 +5599,6 @@
           <t>Arpora</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>ARPORA</t>
@@ -5709,7 +5644,6 @@
           <t>Assagao</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>ASGAON</t>
@@ -5745,6 +5679,11 @@
       <c r="P110" s="2" t="n"/>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Fullyanchem Gaon</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5765,7 +5704,6 @@
           <t>Assonora</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>ASNODE</t>
@@ -5816,7 +5754,6 @@
           <t>Bastora</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -5892,6 +5829,11 @@
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="n"/>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Kolongutt</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5912,7 +5854,6 @@
           <t>Calvim</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>KALVI</t>
@@ -5958,7 +5899,6 @@
           <t>Camurlim</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>OGALI</t>
@@ -6004,7 +5944,6 @@
           <t>Canca</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -6150,7 +6089,6 @@
           <t>Corjuem</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>KHORUJUVEN</t>
@@ -6201,7 +6139,6 @@
           <t>Corlim</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -6237,7 +6174,6 @@
           <t>Cunchelim</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -6333,7 +6269,6 @@
           <t>Marna</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>SHIVOLI</t>
@@ -6384,7 +6319,6 @@
           <t>Marra</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>MARRA</t>
@@ -6430,7 +6364,6 @@
           <t>Mhapsa</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -6521,7 +6454,6 @@
           <t>Moitem</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>PIRNA</t>
@@ -6572,7 +6504,6 @@
           <t>Nachinola</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>NACHINALA</t>
@@ -6618,7 +6549,6 @@
           <t>Nadora</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>NEDORA</t>
@@ -6664,7 +6594,6 @@
           <t>Nagoa</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>NAGVA</t>
@@ -6775,7 +6704,6 @@
           <t>Olaulim</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>VOLAWALI</t>
@@ -6821,7 +6749,6 @@
           <t>Oxel</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>OSHAL</t>
@@ -6872,7 +6799,6 @@
           <t>Paliem</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>PALIYE</t>
@@ -6918,7 +6844,6 @@
           <t>Parra</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>PARRA</t>
@@ -7074,7 +6999,6 @@
           <t>Pirna</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7110,7 +7034,6 @@
           <t>Pomburpa</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>POMBURPA</t>
@@ -7161,7 +7084,6 @@
           <t>Ponolem</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7197,7 +7119,6 @@
           <t>Punola</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7233,7 +7154,6 @@
           <t>Reis-Magos</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7269,7 +7189,6 @@
           <t>Revora</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7415,7 +7334,6 @@
           <t>Sangolda</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>SANGOLDA</t>
@@ -7521,7 +7439,6 @@
           <t>Sircaim</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>SIRSAI</t>
@@ -7627,7 +7544,6 @@
           <t>Tivim</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>DAT</t>
@@ -7678,7 +7594,6 @@
           <t>Ucassaim</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>UKSAI</t>
@@ -7724,7 +7639,6 @@
           <t>Verla</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>PARRA</t>
@@ -7775,7 +7689,6 @@
           <t>Adwalpale</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>ADVALPAL</t>
@@ -7826,7 +7739,6 @@
           <t>Amone</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>AMONA</t>
@@ -7872,7 +7784,6 @@
           <t>Arvalem</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7908,7 +7819,6 @@
           <t>Aturli</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>ATURLI</t>
@@ -7959,7 +7869,6 @@
           <t>Bicholim</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -7975,6 +7884,11 @@
       <c r="P157" s="2" t="n"/>
       <c r="Q157" s="2" t="n"/>
       <c r="R157" s="2" t="n"/>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Divchali</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7995,7 +7909,6 @@
           <t>Bordem</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -8086,7 +7999,6 @@
           <t>Cotombi</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>KOTAMBI</t>
@@ -8132,7 +8044,6 @@
           <t>Cudnem</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>KUDNE</t>
@@ -8183,7 +8094,6 @@
           <t>Curchirem</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>KUDCHIRE</t>
@@ -8229,7 +8139,6 @@
           <t>Dumacem</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>DUMASE</t>
@@ -8280,7 +8189,6 @@
           <t>Lamgao</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -8316,7 +8224,6 @@
           <t>Latambarcem</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>KASARPAL</t>
@@ -8362,7 +8269,6 @@
           <t>Maem</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>BHATWADI</t>
@@ -8393,6 +8299,11 @@
       <c r="P166" s="2" t="n"/>
       <c r="Q166" s="2" t="n"/>
       <c r="R166" s="2" t="n"/>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Mayem</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8413,7 +8324,6 @@
           <t>Maulinguem South</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -8449,7 +8359,6 @@
           <t>Maulinguem-North</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>MAVLINGE</t>
@@ -8495,7 +8404,6 @@
           <t>Mencurem</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>MENKURE</t>
@@ -8541,7 +8449,6 @@
           <t>Mulgao</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>MULGAON</t>
@@ -8587,13 +8494,11 @@
           <t>Naroa</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>NARVA</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
           <t>नार्वें</t>
@@ -8634,7 +8539,6 @@
           <t>Navelim</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>BHARINBAG</t>
@@ -8685,7 +8589,6 @@
           <t>Ona</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>ON</t>
@@ -8796,7 +8699,6 @@
           <t>Piligao</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>PILIGAON</t>
@@ -8842,7 +8744,6 @@
           <t>Salem</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>SAL</t>
@@ -8888,7 +8789,6 @@
           <t>Sankhali</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -8924,7 +8824,6 @@
           <t>Sarvona</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>SARVAN</t>
@@ -8975,7 +8874,6 @@
           <t>Sirigao</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -9011,7 +8909,6 @@
           <t>Surla</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>DINGNASUR</t>
@@ -9057,7 +8954,6 @@
           <t>Vainguinim</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>VAYANGNE</t>
@@ -9103,7 +8999,6 @@
           <t>Velguem</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>VELGE</t>
@@ -9154,7 +9049,6 @@
           <t>Virdi</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -9190,7 +9084,6 @@
           <t>Agarvado</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>AGARVADA</t>
@@ -9241,7 +9134,6 @@
           <t>Alorna</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>ALORNA</t>
@@ -9287,7 +9179,6 @@
           <t>Amberem</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -9378,7 +9269,6 @@
           <t>Cansarvornem</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>KASARVARNE</t>
@@ -9429,7 +9319,6 @@
           <t>Casnem</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -9465,7 +9354,6 @@
           <t>Chandel</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>CHANDEL</t>
@@ -9511,7 +9399,6 @@
           <t>Chopdem</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -9547,7 +9434,6 @@
           <t>Corgao</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>KORGAON</t>
@@ -9593,7 +9479,6 @@
           <t>Dargalim</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>DHARGAL</t>
@@ -9644,7 +9529,6 @@
           <t>Ibrampur</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>IBRAMPUR</t>
@@ -9735,6 +9619,11 @@
       <c r="P195" s="2" t="n"/>
       <c r="Q195" s="2" t="n"/>
       <c r="R195" s="2" t="n"/>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Mandre</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9755,7 +9644,6 @@
           <t>Mopa</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>MOPA</t>
@@ -9811,7 +9699,6 @@
           <t>Morgim</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>MORJIM</t>
@@ -9867,7 +9754,6 @@
           <t>Ozorim</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>VAJRI</t>
@@ -9913,7 +9799,6 @@
           <t>Paliem</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>PALIEM</t>
@@ -10019,7 +9904,6 @@
           <t>Pernem</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -10055,7 +9939,6 @@
           <t>Poroscodem</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>PARASKAD</t>
@@ -10101,7 +9984,6 @@
           <t>Querim</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>QUERIM</t>
@@ -10147,7 +10029,6 @@
           <t>Tamboxem</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>TAMBOSE</t>
@@ -10198,7 +10079,6 @@
           <t>Tiracol</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>TIRACOL</t>
@@ -10244,7 +10124,6 @@
           <t>Torxem</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>TORSE</t>
@@ -10290,7 +10169,6 @@
           <t>Tuem</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>TUYE</t>
@@ -10336,7 +10214,6 @@
           <t>Uguem</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>UGUEM</t>
@@ -10382,7 +10259,6 @@
           <t>Varconda</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr">
         <is>
           <t>VARKHAND</t>
@@ -10428,7 +10304,6 @@
           <t>Virnora</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
           <t>VIRNODA</t>
@@ -10479,7 +10354,6 @@
           <t>Advoi</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>ADVAI DESAIWADA</t>
@@ -10525,7 +10399,6 @@
           <t>Ambedem</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
         <is>
           <t>AMBEDE</t>
@@ -10576,7 +10449,6 @@
           <t>Ambeli</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>AMBELI</t>
@@ -10627,7 +10499,6 @@
           <t>Anjunem</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
           <t>ANJUNE</t>
@@ -10673,7 +10544,6 @@
           <t>Ansolem</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -10709,7 +10579,6 @@
           <t>Assodem</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>AASSODE</t>
@@ -10760,7 +10629,6 @@
           <t>Birondem</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>BHIRONDE</t>
@@ -10806,7 +10674,6 @@
           <t>Bombedem</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>BOMBEDE</t>
@@ -10857,7 +10724,6 @@
           <t>Buimpal</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>BHUIPAL</t>
@@ -10908,7 +10774,6 @@
           <t>Carambolim- Brama</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>KARAMBALI BRAMHA</t>
@@ -10954,7 +10819,6 @@
           <t>Carambolim-Buzruco</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>KARAMBALI BUZRUK</t>
@@ -11005,7 +10869,6 @@
           <t>Caranzol</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>KARANZOL</t>
@@ -11051,7 +10914,6 @@
           <t>Choraundem</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>CHARAVADE</t>
@@ -11097,7 +10959,6 @@
           <t>Codal</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>KODAL</t>
@@ -11143,7 +11004,6 @@
           <t>Codiem</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>HASOLE</t>
@@ -11189,7 +11049,6 @@
           <t>Codqui</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>BARAJAN</t>
@@ -11235,7 +11094,6 @@
           <t>Codvol</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>KODAL</t>
@@ -11286,7 +11144,6 @@
           <t>Compordem</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -11322,7 +11179,6 @@
           <t>Conquirem</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -11358,7 +11214,6 @@
           <t>Cotorem</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>KHOTODE</t>
@@ -11409,7 +11264,6 @@
           <t>Cudcem</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -11445,7 +11299,6 @@
           <t>Cumarconda</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>KUMAR KHAND</t>
@@ -11496,7 +11349,6 @@
           <t>Dabem</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -11532,7 +11384,6 @@
           <t>Damocem</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>DHAMSE</t>
@@ -11583,7 +11434,6 @@
           <t>Davem</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>DONGARVADA</t>
@@ -11634,7 +11484,6 @@
           <t>Derodem</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>DERODE</t>
@@ -11685,7 +11534,6 @@
           <t>Dongurli</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>DONGURVADA</t>
@@ -11736,7 +11584,6 @@
           <t>Edorem</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>KOPARDE</t>
@@ -11787,7 +11634,6 @@
           <t>Golauli</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>GOALI</t>
@@ -11833,7 +11679,6 @@
           <t>Gonteli</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>GHONTELI</t>
@@ -11884,7 +11729,6 @@
           <t>Govanem</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
           <t>GAVANE</t>
@@ -11935,7 +11779,6 @@
           <t>Guleli</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
           <t>GULELI</t>
@@ -11986,7 +11829,6 @@
           <t>Gululem</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
           <t>GULLE</t>
@@ -12032,7 +11874,6 @@
           <t>Ivrem-Buzruco</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>IVRE BUDRUK</t>
@@ -12083,7 +11924,6 @@
           <t>Ivrem-Curdo</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr">
         <is>
           <t>IVRE KHURD</t>
@@ -12129,7 +11969,6 @@
           <t>Maloli</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
           <t>MALOLI</t>
@@ -12180,7 +12019,6 @@
           <t>Malpona</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
           <t>MALPON</t>
@@ -12226,7 +12064,6 @@
           <t>Massordem</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -12262,7 +12099,6 @@
           <t>Mauxi</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
           <t>MAUSI</t>
@@ -12308,7 +12144,6 @@
           <t>Melauli</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>MELAVALI</t>
@@ -12359,7 +12194,6 @@
           <t>Morlem</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr">
         <is>
           <t>MORLE</t>
@@ -12410,7 +12244,6 @@
           <t>Nagargao</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -12446,7 +12279,6 @@
           <t>Naguem</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Naguem</t>
@@ -12492,7 +12324,6 @@
           <t>Naneli</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>NANELI</t>
@@ -12543,7 +12374,6 @@
           <t>Nanorem</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>NANODE</t>
@@ -12589,7 +12419,6 @@
           <t>Nanus</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -12680,7 +12509,6 @@
           <t>Padeli</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>BHOMWADI</t>
@@ -12726,7 +12554,6 @@
           <t>Pale</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>PALI</t>
@@ -12777,7 +12604,6 @@
           <t>Pendral</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>PENRAL</t>
@@ -12823,7 +12649,6 @@
           <t>Pissurlem</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>PISSURLE</t>
@@ -12874,7 +12699,6 @@
           <t>Podocem</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>PODSEN</t>
@@ -12920,7 +12744,6 @@
           <t>Ponocem</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>PANSE</t>
@@ -12966,7 +12789,6 @@
           <t>Ponsuli</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -13002,7 +12824,6 @@
           <t>Poriem</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>PARIYE</t>
@@ -13048,7 +12869,6 @@
           <t>Quelaudem</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>KELAVADE</t>
@@ -13094,7 +12914,6 @@
           <t>Querim</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>BAYALVADA</t>
@@ -13140,7 +12959,6 @@
           <t>Ravona</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>RAVAN</t>
@@ -13186,7 +13004,6 @@
           <t>Rivem</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>RIVE</t>
@@ -13232,7 +13049,6 @@
           <t>Saleli</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>SALILI</t>
@@ -13278,7 +13094,6 @@
           <t>Sanvorcem</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>SANVARSHE</t>
@@ -13324,7 +13139,6 @@
           <t>Sanvordem</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>SANVARDE</t>
@@ -13375,7 +13189,6 @@
           <t>Satorem</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>HEDODE</t>
@@ -13426,7 +13239,6 @@
           <t>Satrem</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>SATRE</t>
@@ -13472,7 +13284,6 @@
           <t>Sigonem</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>SINGNA</t>
@@ -13518,7 +13329,6 @@
           <t>Siranguli</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -13554,7 +13364,6 @@
           <t>Siroli</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>SHIROLI</t>
@@ -13605,7 +13414,6 @@
           <t>Sirsodem</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>SIRSODE</t>
@@ -13651,7 +13459,6 @@
           <t>Sonal</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>SONAL</t>
@@ -13697,7 +13504,6 @@
           <t>Sonus-Vonvoliem</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>OVALAYEN</t>
@@ -13743,7 +13549,6 @@
           <t>Surla</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>SURLA</t>
@@ -13789,7 +13594,6 @@
           <t>Ustem</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>USTE</t>
@@ -13840,7 +13644,6 @@
           <t>Vaguriem</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>WAGURE</t>
@@ -13886,7 +13689,6 @@
           <t>Vainguinim</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>VAYANGANI</t>
@@ -13932,7 +13734,6 @@
           <t>Valpoi</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
       <c r="L285" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -13968,7 +13769,6 @@
           <t>Vantem</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>VANTE GAONKARWADA</t>
@@ -14014,7 +13814,6 @@
           <t>Velguem</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>VELGUE</t>
@@ -14060,7 +13859,6 @@
           <t>Velus</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -14096,7 +13894,6 @@
           <t>Xelopo-Buzruco</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>SALPI BUDRUK</t>
@@ -14142,7 +13939,6 @@
           <t>Xelopo-Curdo</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>SHELPI KHURD</t>
@@ -14193,7 +13989,6 @@
           <t>Zarani</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
       <c r="L291" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -14229,7 +14024,6 @@
           <t>Zormen</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>JARMA</t>
@@ -14275,7 +14069,6 @@
           <t>Ambarim</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -14311,7 +14104,6 @@
           <t>Azossim</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>AJOSI</t>
@@ -14357,7 +14149,6 @@
           <t>Bainguinim</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>BAINGINI</t>
@@ -14463,7 +14254,6 @@
           <t>Batim</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
       <c r="L297" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -14554,7 +14344,6 @@
           <t>Capao</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>VANSHI</t>
@@ -14600,7 +14389,6 @@
           <t>Caraim</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>MADEL</t>
@@ -14646,7 +14434,6 @@
           <t>Carambolim</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>KARMALI</t>
@@ -14752,7 +14539,6 @@
           <t>Chorao</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -14768,6 +14554,11 @@
       <c r="P303" s="2" t="n"/>
       <c r="Q303" s="2" t="n"/>
       <c r="R303" s="2" t="n"/>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Choddnnem</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -14948,7 +14739,6 @@
           <t>Curca</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>KURKA</t>
@@ -14994,7 +14784,6 @@
           <t>Durgavado</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
       <c r="L308" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -15030,7 +14819,6 @@
           <t>Ella</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>VELA</t>
@@ -15081,7 +14869,6 @@
           <t>Gancim</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>GANSIM</t>
@@ -15127,7 +14914,6 @@
           <t>Gandaulim</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -15143,6 +14929,11 @@
       <c r="P311" s="2" t="n"/>
       <c r="Q311" s="2" t="n"/>
       <c r="R311" s="2" t="n"/>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Gaundale</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -15163,7 +14954,6 @@
           <t>Goa-Velha</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>GOA VELHA</t>
@@ -15194,6 +14984,11 @@
       <c r="P312" s="2" t="n"/>
       <c r="Q312" s="2" t="n"/>
       <c r="R312" s="2" t="n"/>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>Vhoddlem Goem</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -15214,7 +15009,6 @@
           <t>Goalim-Moula</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>GOALIM MOVLA</t>
@@ -15260,7 +15054,6 @@
           <t>Goltim</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>GOLTIM</t>
@@ -15361,7 +15154,6 @@
           <t>Malar</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>MALAR</t>
@@ -15407,7 +15199,6 @@
           <t>Mandur</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>MANUR</t>
@@ -15433,6 +15224,11 @@
       <c r="P317" s="2" t="n"/>
       <c r="Q317" s="2" t="n"/>
       <c r="R317" s="2" t="n"/>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Mandura</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -15648,7 +15444,6 @@
           <t>Naroa</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -15684,7 +15479,6 @@
           <t>Navelim</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>NAVELI</t>
@@ -15740,7 +15534,6 @@
           <t>Neura-O-Grande</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
       <c r="F324" t="inlineStr">
         <is>
           <t>NEVRA GRANDE</t>
@@ -15786,7 +15579,6 @@
           <t>Neura-O-Pequeno</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
       <c r="F325" t="inlineStr">
         <is>
           <t>NEVRA PIKNE</t>
@@ -15832,7 +15624,6 @@
           <t>Panaji</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -15948,7 +15739,6 @@
           <t>Siridao</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr">
         <is>
           <t>SIRIDAO</t>
@@ -15994,7 +15784,6 @@
           <t>Talaulim</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr">
         <is>
           <t>TALAUIM</t>
@@ -16040,7 +15829,6 @@
           <t>Taleigao</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr">
         <is>
           <t>DURGAVADO</t>
@@ -16086,7 +15874,6 @@
           <t>Arossim</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr">
         <is>
           <t>AROSIM</t>
@@ -16137,7 +15924,6 @@
           <t>Cansaulim</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr">
         <is>
           <t>KANSAVLIM</t>
@@ -16243,7 +16029,6 @@
           <t>Chicolna</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr">
         <is>
           <t>CHIKOLNA</t>
@@ -16349,7 +16134,6 @@
           <t>Cuelim</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -16385,7 +16169,6 @@
           <t>Dabolim</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>IJORSHI</t>
@@ -16446,7 +16229,6 @@
           <t>Issorcim</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
           <t>IJORSHI</t>
@@ -16497,7 +16279,6 @@
           <t>Mormugao Port</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -16533,7 +16314,6 @@
           <t>Pale</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
           <t>PALI</t>
@@ -16584,7 +16364,6 @@
           <t>Quelossim</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
           <t>KELOSIM</t>
@@ -16635,7 +16414,6 @@
           <t>Sambhaji</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -16731,7 +16509,6 @@
           <t>Sao Jacinto Island</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -16767,7 +16544,6 @@
           <t>Sao Jorge Island</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -16803,7 +16579,6 @@
           <t>Vadem</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -16839,7 +16614,6 @@
           <t>Velsao</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
           <t>VELSAVAON</t>
@@ -16885,7 +16659,6 @@
           <t>Adcolna</t>
         </is>
       </c>
-      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
           <t>HADKON</t>
@@ -16986,7 +16759,6 @@
           <t>Betora</t>
         </is>
       </c>
-      <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr">
         <is>
           <t>BETORA</t>
@@ -17032,7 +16804,6 @@
           <t>Betqui</t>
         </is>
       </c>
-      <c r="E352" t="inlineStr"/>
       <c r="F352" t="inlineStr">
         <is>
           <t>BETGI</t>
@@ -17083,7 +16854,6 @@
           <t>Boma</t>
         </is>
       </c>
-      <c r="E353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -17179,7 +16949,6 @@
           <t>Candepar</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr">
         <is>
           <t>KHANDEPAR</t>
@@ -17280,7 +17049,6 @@
           <t>Codar</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr">
         <is>
           <t>KODAR</t>
@@ -17331,7 +17099,6 @@
           <t>Conxem</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr">
         <is>
           <t>KONSEN</t>
@@ -17382,7 +17149,6 @@
           <t>Cuncoliem</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr">
         <is>
           <t>KUNKULE</t>
@@ -17428,7 +17194,6 @@
           <t>Cundaim</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr">
         <is>
           <t>KUNDAI</t>
@@ -17514,7 +17279,6 @@
           <t>Durbhat</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr">
         <is>
           <t>DURBHAT</t>
@@ -17560,7 +17324,6 @@
           <t>Gangem</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr">
         <is>
           <t>GOTIAKHADILWADA</t>
@@ -17666,7 +17429,6 @@
           <t>Nirancal</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr">
         <is>
           <t>KALSAI</t>
@@ -17752,7 +17514,6 @@
           <t>Ponchavadi</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr">
         <is>
           <t>P A N C H V A D I</t>
@@ -17803,7 +17564,6 @@
           <t>Ponda</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -17899,7 +17659,6 @@
           <t>Querim</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
           <t>KERI</t>
@@ -17945,7 +17704,6 @@
           <t>Queula</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -17981,7 +17739,6 @@
           <t>Savoi-Verem</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
           <t>PONDA</t>
@@ -18037,7 +17794,6 @@
           <t>Shiroda</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
           <t>SHIRODA</t>
@@ -18088,7 +17844,6 @@
           <t>Telaulim</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>AGAPUR</t>
@@ -18139,7 +17894,6 @@
           <t>Tivrem</t>
         </is>
       </c>
-      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>TIVREN</t>
@@ -18240,7 +17994,6 @@
           <t>Vadi</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
           <t>WADI</t>
@@ -18286,7 +18039,6 @@
           <t>Vagurbem</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
           <t>KHAJANWADA</t>
@@ -18332,7 +18084,6 @@
           <t>Velinga</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
           <t>VELING</t>
@@ -18378,7 +18129,6 @@
           <t>Volvoi</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
           <t>VALVAI</t>
@@ -18429,7 +18179,6 @@
           <t>Adsulim</t>
         </is>
       </c>
-      <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
           <t>ADSULI</t>
@@ -18475,7 +18224,6 @@
           <t>Ambelim</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -18511,7 +18259,6 @@
           <t>Aquem-Baixo</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
           <t>AKE</t>
@@ -18562,7 +18309,6 @@
           <t>Assolna</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
           <t>ASSOLNA</t>
@@ -18653,6 +18399,11 @@
       <c r="P385" s="2" t="n"/>
       <c r="Q385" s="2" t="n"/>
       <c r="R385" s="2" t="n"/>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>Banavalli</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -18673,7 +18424,6 @@
           <t>Betalbatim</t>
         </is>
       </c>
-      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
           <t>BTALBHATI</t>
@@ -18704,6 +18454,11 @@
       <c r="P386" s="2" t="n"/>
       <c r="Q386" s="2" t="n"/>
       <c r="R386" s="2" t="n"/>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>Betpatte</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -18724,7 +18479,6 @@
           <t>Calata</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
           <t>GIRIM</t>
@@ -18770,7 +18524,6 @@
           <t>Camurlim</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
           <t>KAMARLIM</t>
@@ -18816,7 +18569,6 @@
           <t>Cana</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
           <t>KANA</t>
@@ -18867,7 +18619,6 @@
           <t>Carmona</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
           <t>KARMANE</t>
@@ -18918,7 +18669,6 @@
           <t>Cavelossim</t>
         </is>
       </c>
-      <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
           <t>KAVLESI</t>
@@ -18964,7 +18714,6 @@
           <t>Cavorim</t>
         </is>
       </c>
-      <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
           <t>KAVORIN</t>
@@ -19010,7 +18759,6 @@
           <t>Chandor</t>
         </is>
       </c>
-      <c r="E393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -19081,6 +18829,11 @@
       <c r="P394" s="2" t="n"/>
       <c r="Q394" s="2" t="n"/>
       <c r="R394" s="2" t="n"/>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>Chinchone</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -19101,7 +18854,6 @@
           <t>Colva</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
           <t>KOLVE</t>
@@ -19147,7 +18899,6 @@
           <t>Cuncolim</t>
         </is>
       </c>
-      <c r="E396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -19298,7 +19049,6 @@
           <t>Deussua</t>
         </is>
       </c>
-      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
           <t>DEVSUA</t>
@@ -19344,7 +19094,6 @@
           <t>Dicarpale</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
           <t>DIKARPAL</t>
@@ -19395,7 +19144,6 @@
           <t>Dramapur</t>
         </is>
       </c>
-      <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
           <t>DRAMAPUR</t>
@@ -19446,7 +19194,6 @@
           <t>Duncolim</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
           <t>DHUNKALI</t>
@@ -19492,7 +19239,6 @@
           <t>Gaundaulim</t>
         </is>
       </c>
-      <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
           <t>GANDAVLI</t>
@@ -19538,7 +19284,6 @@
           <t>Gonsua</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
           <t>GANSUA</t>
@@ -19584,7 +19329,6 @@
           <t>Guirdolim</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
           <t>GIRDOLIN</t>
@@ -19635,7 +19379,6 @@
           <t>Loutulim</t>
         </is>
       </c>
-      <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
           <t>RASAAIN</t>
@@ -19681,7 +19424,6 @@
           <t>Macasana</t>
         </is>
       </c>
-      <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
           <t>MAKAZAN</t>
@@ -19727,7 +19469,6 @@
           <t>Majorda</t>
         </is>
       </c>
-      <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
           <t>MAJORDA</t>
@@ -19773,7 +19514,6 @@
           <t>Margao</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -19789,6 +19529,11 @@
       <c r="P409" s="2" t="n"/>
       <c r="Q409" s="2" t="n"/>
       <c r="R409" s="2" t="n"/>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>Madgaon</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -19809,7 +19554,6 @@
           <t>Mulem</t>
         </is>
       </c>
-      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
           <t>MULEM</t>
@@ -19855,7 +19599,6 @@
           <t>Nagoa</t>
         </is>
       </c>
-      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
           <t>NAGVE</t>
@@ -20021,7 +19764,6 @@
           <t>Orlim</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
           <t>URLI</t>
@@ -20067,7 +19809,6 @@
           <t>Paroda</t>
         </is>
       </c>
-      <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
           <t>PARODA</t>
@@ -20113,7 +19854,6 @@
           <t>Rachol</t>
         </is>
       </c>
-      <c r="E416" t="inlineStr"/>
       <c r="L416" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -20264,7 +20004,6 @@
           <t>Sarzora</t>
         </is>
       </c>
-      <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
           <t>SARZORA</t>
@@ -20315,7 +20054,6 @@
           <t>Seraulim</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr"/>
       <c r="L420" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -20351,7 +20089,6 @@
           <t>Sernabatim</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
           <t>SERNABATIM</t>
@@ -20397,7 +20134,6 @@
           <t>Sirlim</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr"/>
       <c r="L422" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -20433,7 +20169,6 @@
           <t>Talaulim</t>
         </is>
       </c>
-      <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
           <t>TALAVLI</t>
@@ -20484,7 +20219,6 @@
           <t>Talvorda</t>
         </is>
       </c>
-      <c r="E424" t="inlineStr"/>
       <c r="L424" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -20520,7 +20254,6 @@
           <t>Utorda</t>
         </is>
       </c>
-      <c r="E425" t="inlineStr"/>
       <c r="F425" t="inlineStr">
         <is>
           <t>UTARDA</t>
@@ -20566,7 +20299,6 @@
           <t>Vanelim</t>
         </is>
       </c>
-      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
           <t>VANELI</t>
@@ -20672,7 +20404,6 @@
           <t>Varoda</t>
         </is>
       </c>
-      <c r="E428" t="inlineStr"/>
       <c r="L428" t="inlineStr">
         <is>
           <t>No Konkani source</t>
@@ -20708,7 +20439,6 @@
           <t>Velim</t>
         </is>
       </c>
-      <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr">
         <is>
           <t>GORKOMARAD</t>
@@ -20791,7 +20521,7 @@
       <c r="R430" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R430"/>
+  <autoFilter ref="A1:V430"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/village_names_review.xlsx
+++ b/data/village_names_review.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$B$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review'!$A$1:$V$430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Review'!$A$1:$X$430</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V430"/>
+  <dimension ref="A1:X430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,8 @@
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -672,6 +674,16 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>luis_spelling</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>gazetteer_government</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>gazetteer_soi</t>
         </is>
       </c>
     </row>
@@ -5514,9 +5526,29 @@
       <c r="P107" s="2" t="n"/>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>हळदोणें</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Haldone</t>
+        </is>
+      </c>
       <c r="V107" t="inlineStr">
         <is>
           <t>Oidone</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Aldona</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Aldona</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20553,7 @@
       <c r="R430" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V430"/>
+  <autoFilter ref="A1:X430"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/village_names_review.xlsx
+++ b/data/village_names_review.xlsx
@@ -741,6 +741,31 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>आगोंद</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Agond</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Agonda</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Agonda</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -821,6 +846,31 @@
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>काणकोण</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kankon</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Canacona</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Kankon</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -906,6 +956,26 @@
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Khol</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Cola</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Kola</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -951,6 +1021,26 @@
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Khotigaon</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Cotigao</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Khotigaon</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -996,6 +1086,21 @@
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gaondongre</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Gaundongrem</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1046,6 +1151,31 @@
       <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>लोलये</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Lolye</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Loliem</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Loliem</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1081,6 +1211,16 @@
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Nagarshe-Palole</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1126,6 +1266,31 @@
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>पैंगिण</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Paingin</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Poinguinim</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Poingunin</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1176,6 +1341,26 @@
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>आगलोट</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Aglot</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Aglote</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1221,6 +1406,21 @@
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Bandoli</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bandoli</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1266,6 +1466,21 @@
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
       <c r="R14" s="2" t="n"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kamarkhand</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Camarconda</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1401,9 +1616,24 @@
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="n"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kule</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>Kulem</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Colem</t>
         </is>
       </c>
     </row>
@@ -1441,6 +1671,21 @@
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Karmane</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Karmane</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1486,6 +1731,26 @@
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dharbandode</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Darbandora</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Darbandara</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1531,6 +1796,26 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>मैसाळ</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Mhaisal</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Moissal</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1576,6 +1861,26 @@
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Molem</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Molem</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1611,6 +1916,26 @@
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>पिळयें</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Pilye</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Piliem</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1656,6 +1981,26 @@
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Sankorde</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sancordem</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Sakvorde</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1701,6 +2046,26 @@
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>सांगोडा</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Sangoda</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sangod</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1746,6 +2111,26 @@
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>शिगांव</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Shigaon</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sigao</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1791,6 +2176,31 @@
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>सोनावळी</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Sonavali</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sonauli</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Sanavalin</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1886,6 +2296,26 @@
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>अडणे</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Adne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Adnem</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1936,6 +2366,31 @@
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>आमोलें</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Amole</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ambaulim</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ambavali</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2021,6 +2476,26 @@
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>असोळडें</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Asolde</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Assolda</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2071,6 +2546,21 @@
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Avede</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Avedem</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2121,6 +2611,31 @@
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>बाळ्ळी</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Balli</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Bally</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2171,6 +2686,16 @@
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Barshe</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2221,6 +2746,21 @@
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
       <c r="R35" s="2" t="n"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Benudde</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bendordem</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2256,6 +2796,31 @@
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="n"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>काकोडें</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kakode</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Cacora</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Kakoda</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2336,6 +2901,26 @@
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="n"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kazur</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Cazur</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Kazur</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2381,6 +2966,26 @@
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="n"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>चायफी</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Chaiphi</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Chaifi</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2416,6 +3021,21 @@
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="n"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Khadde</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Cordem</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2461,6 +3081,21 @@
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Karl</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Corla</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2541,6 +3176,26 @@
       <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n"/>
       <c r="R43" s="2" t="n"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kudchade</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Curchorem</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Kudchanden</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2661,6 +3316,26 @@
       <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Fatarpe</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fatorpa</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Fatarpa</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2796,6 +3471,26 @@
       <c r="P49" s="2" t="n"/>
       <c r="Q49" s="2" t="n"/>
       <c r="R49" s="2" t="n"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Mayna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Maina</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Mayna</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2841,6 +3536,26 @@
       <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="n"/>
       <c r="R50" s="2" t="n"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>मांगाळ</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Mangal</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mangal</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2886,6 +3601,21 @@
       <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="n"/>
       <c r="R51" s="2" t="n"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Malakpan</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Molcopona</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2971,6 +3701,21 @@
       <c r="P53" s="2" t="n"/>
       <c r="Q53" s="2" t="n"/>
       <c r="R53" s="2" t="n"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Morpirl</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Morpirla</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3116,6 +3861,31 @@
       <c r="P56" s="2" t="n"/>
       <c r="Q56" s="2" t="n"/>
       <c r="R56" s="2" t="n"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>पाडी</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Padi</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Padi</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Padi</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3166,6 +3936,26 @@
       <c r="P57" s="2" t="n"/>
       <c r="Q57" s="2" t="n"/>
       <c r="R57" s="2" t="n"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Pirl</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Pirla</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Pirl</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3216,6 +4006,21 @@
       <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="n"/>
       <c r="R58" s="2" t="n"/>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Khede</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Quedem</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3251,6 +4056,31 @@
       <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="2" t="n"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>केपें</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kepe</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Quepem</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Quepem</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3296,6 +4126,26 @@
       <c r="P60" s="2" t="n"/>
       <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="n"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>किस्कोण</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kiskon</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Quisconda</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3341,6 +4191,26 @@
       <c r="P61" s="2" t="n"/>
       <c r="Q61" s="2" t="n"/>
       <c r="R61" s="2" t="n"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>किटोळ</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kital</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Quitol</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3391,6 +4261,26 @@
       <c r="P62" s="2" t="n"/>
       <c r="Q62" s="2" t="n"/>
       <c r="R62" s="2" t="n"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>शिरवय</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Shirvai</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sirvoi</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3436,6 +4326,26 @@
       <c r="P63" s="2" t="n"/>
       <c r="Q63" s="2" t="n"/>
       <c r="R63" s="2" t="n"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Sulkarn</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sulcorna</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Surkarn</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3471,6 +4381,21 @@
       <c r="P64" s="2" t="n"/>
       <c r="Q64" s="2" t="n"/>
       <c r="R64" s="2" t="n"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Telloi</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Tiloi</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3516,6 +4441,21 @@
       <c r="P65" s="2" t="n"/>
       <c r="Q65" s="2" t="n"/>
       <c r="R65" s="2" t="n"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Hunanna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Undorna</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3576,6 +4516,21 @@
       <c r="P66" s="2" t="n"/>
       <c r="Q66" s="2" t="n"/>
       <c r="R66" s="2" t="n"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Shelde</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Xeldem</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3611,6 +4566,21 @@
       <c r="P67" s="2" t="n"/>
       <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="n"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Shelvan</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Xelvona</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3711,6 +4681,21 @@
       <c r="P69" s="2" t="n"/>
       <c r="Q69" s="2" t="n"/>
       <c r="R69" s="2" t="n"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Zanode</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Zanodem</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3756,6 +4741,21 @@
       <c r="P70" s="2" t="n"/>
       <c r="Q70" s="2" t="n"/>
       <c r="R70" s="2" t="n"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>हांतरये</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Antoriem</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3806,6 +4806,31 @@
       <c r="P71" s="2" t="n"/>
       <c r="Q71" s="2" t="n"/>
       <c r="R71" s="2" t="n"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>भाटी</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Bhati</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Bati</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Bhati</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3896,6 +4921,26 @@
       <c r="P73" s="2" t="n"/>
       <c r="Q73" s="2" t="n"/>
       <c r="R73" s="2" t="n"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Calem</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Kale</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4086,6 +5131,21 @@
       <c r="P77" s="2" t="n"/>
       <c r="Q77" s="2" t="n"/>
       <c r="R77" s="2" t="n"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Kashti</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Costi</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4131,6 +5191,21 @@
       <c r="P78" s="2" t="n"/>
       <c r="Q78" s="2" t="n"/>
       <c r="R78" s="2" t="n"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Kotarli</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Cotarli</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4176,6 +5251,26 @@
       <c r="P79" s="2" t="n"/>
       <c r="Q79" s="2" t="n"/>
       <c r="R79" s="2" t="n"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Kumari</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Cumbari</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Kumbharin</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4276,6 +5371,26 @@
       <c r="P81" s="2" t="n"/>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="n"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>डोंगर</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dongar</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dongor</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4321,6 +5436,21 @@
       <c r="P82" s="2" t="n"/>
       <c r="Q82" s="2" t="n"/>
       <c r="R82" s="2" t="n"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dongurli</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dongurli</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4516,6 +5646,21 @@
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="n"/>
       <c r="R86" s="2" t="n"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Mugulli</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Muguli</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4561,6 +5706,21 @@
       <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="n"/>
       <c r="R87" s="2" t="n"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Naikini</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Naiquinim</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4656,6 +5816,21 @@
       <c r="P89" s="2" t="n"/>
       <c r="Q89" s="2" t="n"/>
       <c r="R89" s="2" t="n"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Nunde</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Nundem</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4746,6 +5921,26 @@
       <c r="P91" s="2" t="n"/>
       <c r="Q91" s="2" t="n"/>
       <c r="R91" s="2" t="n"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>पाटयें</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Patye</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Patiem</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4791,6 +5986,21 @@
       <c r="P92" s="2" t="n"/>
       <c r="Q92" s="2" t="n"/>
       <c r="R92" s="2" t="n"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Patte</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Porteem</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4836,6 +6046,21 @@
       <c r="P93" s="2" t="n"/>
       <c r="Q93" s="2" t="n"/>
       <c r="R93" s="2" t="n"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Patre</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Potrem</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4891,6 +6116,31 @@
       <c r="P94" s="2" t="n"/>
       <c r="Q94" s="2" t="n"/>
       <c r="R94" s="2" t="n"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>रिवण</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Rivan</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Rivona</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Rivon</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4941,6 +6191,21 @@
       <c r="P95" s="2" t="n"/>
       <c r="Q95" s="2" t="n"/>
       <c r="R95" s="2" t="n"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Rumde</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Rumbrem</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5021,6 +6286,31 @@
       <c r="P97" s="2" t="n"/>
       <c r="Q97" s="2" t="n"/>
       <c r="R97" s="2" t="n"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>सांगे</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Sange</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Sanguem</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Sanguem</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5066,6 +6356,26 @@
       <c r="P98" s="2" t="n"/>
       <c r="Q98" s="2" t="n"/>
       <c r="R98" s="2" t="n"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>सांतोण</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Santan</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Santona</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5316,6 +6626,26 @@
       <c r="P103" s="2" t="n"/>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="n"/>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Verle</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Verlem</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Verlem</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5366,6 +6696,21 @@
       <c r="P104" s="2" t="n"/>
       <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="n"/>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Vichundre</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Vichundrem</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5411,6 +6756,21 @@
       <c r="P105" s="2" t="n"/>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="n"/>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Vilayana</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Viliena</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5606,9 +6966,29 @@
       <c r="P108" s="2" t="n"/>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="n"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>हणजूण</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr">
         <is>
           <t>Honjunnem</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Anjuna</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Anjuna</t>
         </is>
       </c>
     </row>
@@ -5711,9 +7091,29 @@
       <c r="P110" s="2" t="n"/>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Asgaon</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
       <c r="V110" t="inlineStr">
         <is>
           <t>Fullyanchem Gaon</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Assagao</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Asgaon</t>
         </is>
       </c>
     </row>
@@ -5766,6 +7166,21 @@
       <c r="P111" s="2" t="n"/>
       <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="n"/>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Asnode</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Assonora</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5801,6 +7216,26 @@
       <c r="P112" s="2" t="n"/>
       <c r="Q112" s="2" t="n"/>
       <c r="R112" s="2" t="n"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Bastode</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bastora</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Bastora</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5861,9 +7296,29 @@
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="n"/>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Kalangut</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr">
         <is>
           <t>Kolongutt</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Calangute</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Kalangut</t>
         </is>
       </c>
     </row>
@@ -5911,6 +7366,31 @@
       <c r="P114" s="2" t="n"/>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="n"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>कालवी</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Kalvi</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Calvim</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Kalvi</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5956,6 +7436,26 @@
       <c r="P115" s="2" t="n"/>
       <c r="Q115" s="2" t="n"/>
       <c r="R115" s="2" t="n"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>कामुर्ली</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Camurlim</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Kamurli</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -6046,6 +7546,26 @@
       <c r="P117" s="2" t="n"/>
       <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="n"/>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Kandoli</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Candolim</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Kandoli</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6101,6 +7621,31 @@
       <c r="P118" s="2" t="n"/>
       <c r="Q118" s="2" t="n"/>
       <c r="R118" s="2" t="n"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>कोलवाळ</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Kolval</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Colvale</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Kolval</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6151,6 +7696,21 @@
       <c r="P119" s="2" t="n"/>
       <c r="Q119" s="2" t="n"/>
       <c r="R119" s="2" t="n"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Khorjuve</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Corjuem</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6221,6 +7781,21 @@
       <c r="P121" s="2" t="n"/>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="2" t="n"/>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Kucheli</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Cunchelim</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6281,6 +7856,16 @@
       <c r="P122" s="2" t="n"/>
       <c r="Q122" s="2" t="n"/>
       <c r="R122" s="2" t="n"/>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Guirim</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6331,6 +7916,21 @@
       <c r="P123" s="2" t="n"/>
       <c r="Q123" s="2" t="n"/>
       <c r="R123" s="2" t="n"/>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Marne</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Marna</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6716,6 +8316,26 @@
       <c r="P131" s="2" t="n"/>
       <c r="Q131" s="2" t="n"/>
       <c r="R131" s="2" t="n"/>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Nerul</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Nerul</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Nerul</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6811,6 +8431,26 @@
       <c r="P133" s="2" t="n"/>
       <c r="Q133" s="2" t="n"/>
       <c r="R133" s="2" t="n"/>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Oshel</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Oxel</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Oshal</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6901,6 +8541,26 @@
       <c r="P135" s="2" t="n"/>
       <c r="Q135" s="2" t="n"/>
       <c r="R135" s="2" t="n"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>पर्रा</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Parra</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Parra</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7011,6 +8671,26 @@
       <c r="P137" s="2" t="n"/>
       <c r="Q137" s="2" t="n"/>
       <c r="R137" s="2" t="n"/>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Pilarn</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Pilerne</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Pilerne</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7046,6 +8726,26 @@
       <c r="P138" s="2" t="n"/>
       <c r="Q138" s="2" t="n"/>
       <c r="R138" s="2" t="n"/>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Pirna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Pirna</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Perne</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7201,6 +8901,21 @@
       <c r="P142" s="2" t="n"/>
       <c r="Q142" s="2" t="n"/>
       <c r="R142" s="2" t="n"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Reis Magos</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Reis Magos</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7291,6 +9006,26 @@
       <c r="P144" s="2" t="n"/>
       <c r="Q144" s="2" t="n"/>
       <c r="R144" s="2" t="n"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Salgaon</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Saligao</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Saligao</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7391,6 +9126,21 @@
       <c r="P146" s="2" t="n"/>
       <c r="Q146" s="2" t="n"/>
       <c r="R146" s="2" t="n"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Sangodde</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Sangolda</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7451,6 +9201,26 @@
       <c r="P147" s="2" t="n"/>
       <c r="Q147" s="2" t="n"/>
       <c r="R147" s="2" t="n"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Shivoli</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Siolim</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Sioli</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7556,6 +9326,21 @@
       <c r="P149" s="2" t="n"/>
       <c r="Q149" s="2" t="n"/>
       <c r="R149" s="2" t="n"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Sukur</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Socorro</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7701,6 +9486,26 @@
       <c r="P152" s="2" t="n"/>
       <c r="Q152" s="2" t="n"/>
       <c r="R152" s="2" t="n"/>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Verle</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Verla</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Verlem</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7751,6 +9556,31 @@
       <c r="P153" s="2" t="n"/>
       <c r="Q153" s="2" t="n"/>
       <c r="R153" s="2" t="n"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>अडवलपाल</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Advalpal</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Adwalpale</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Advalpal</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7831,6 +9661,26 @@
       <c r="P155" s="2" t="n"/>
       <c r="Q155" s="2" t="n"/>
       <c r="R155" s="2" t="n"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>हरवळें</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Harvale</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Arvalem</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7881,6 +9731,21 @@
       <c r="P156" s="2" t="n"/>
       <c r="Q156" s="2" t="n"/>
       <c r="R156" s="2" t="n"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>हातुर्ली</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Aturli</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7916,9 +9781,24 @@
       <c r="P157" s="2" t="n"/>
       <c r="Q157" s="2" t="n"/>
       <c r="R157" s="2" t="n"/>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Dicholi</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
       <c r="V157" t="inlineStr">
         <is>
           <t>Divchali</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Dicholi</t>
         </is>
       </c>
     </row>
@@ -8011,6 +9891,31 @@
       <c r="P159" s="2" t="n"/>
       <c r="Q159" s="2" t="n"/>
       <c r="R159" s="2" t="n"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>कारापूर</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Karapur</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Carapur</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Karapur</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8106,6 +10011,21 @@
       <c r="P161" s="2" t="n"/>
       <c r="Q161" s="2" t="n"/>
       <c r="R161" s="2" t="n"/>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Kudne</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Cudnem</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8151,6 +10071,21 @@
       <c r="P162" s="2" t="n"/>
       <c r="Q162" s="2" t="n"/>
       <c r="R162" s="2" t="n"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Kudchire</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Curchirem</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8201,6 +10136,26 @@
       <c r="P163" s="2" t="n"/>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="n"/>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Dhumashe</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Dumacem</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Dumase</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8281,6 +10236,21 @@
       <c r="P165" s="2" t="n"/>
       <c r="Q165" s="2" t="n"/>
       <c r="R165" s="2" t="n"/>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Lathambarshe</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Latambarcem</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8331,7 +10301,27 @@
       <c r="P166" s="2" t="n"/>
       <c r="Q166" s="2" t="n"/>
       <c r="R166" s="2" t="n"/>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Maye</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
       <c r="V166" t="inlineStr">
+        <is>
+          <t>Mayem</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Maem</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
         <is>
           <t>Mayem</t>
         </is>
@@ -8461,6 +10451,21 @@
       <c r="P169" s="2" t="n"/>
       <c r="Q169" s="2" t="n"/>
       <c r="R169" s="2" t="n"/>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Menkure</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Mencurem</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8506,6 +10511,26 @@
       <c r="P170" s="2" t="n"/>
       <c r="Q170" s="2" t="n"/>
       <c r="R170" s="2" t="n"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>मुळगांव</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Mulgaon</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Mulgao</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8756,6 +10781,21 @@
       <c r="P175" s="2" t="n"/>
       <c r="Q175" s="2" t="n"/>
       <c r="R175" s="2" t="n"/>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Piligao</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Piligaon</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8801,6 +10841,31 @@
       <c r="P176" s="2" t="n"/>
       <c r="Q176" s="2" t="n"/>
       <c r="R176" s="2" t="n"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>साळ</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>Sal</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8886,6 +10951,26 @@
       <c r="P178" s="2" t="n"/>
       <c r="Q178" s="2" t="n"/>
       <c r="R178" s="2" t="n"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>सरवण</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Sarvan</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Sarvona</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8921,6 +11006,31 @@
       <c r="P179" s="2" t="n"/>
       <c r="Q179" s="2" t="n"/>
       <c r="R179" s="2" t="n"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>शिरगांव</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Shirgaon</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Sirigao</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Shrigaon</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9011,6 +11121,21 @@
       <c r="P181" s="2" t="n"/>
       <c r="Q181" s="2" t="n"/>
       <c r="R181" s="2" t="n"/>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Vainguinim</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Vayangani</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9096,6 +11221,26 @@
       <c r="P183" s="2" t="n"/>
       <c r="Q183" s="2" t="n"/>
       <c r="R183" s="2" t="n"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>विर्डी</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Virdi</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Virdi</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9146,6 +11291,16 @@
       <c r="P184" s="2" t="n"/>
       <c r="Q184" s="2" t="n"/>
       <c r="R184" s="2" t="n"/>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Agarvado</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9191,6 +11346,26 @@
       <c r="P185" s="2" t="n"/>
       <c r="Q185" s="2" t="n"/>
       <c r="R185" s="2" t="n"/>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Halarn</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Alorna</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>Alorna</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9226,6 +11401,21 @@
       <c r="P186" s="2" t="n"/>
       <c r="Q186" s="2" t="n"/>
       <c r="R186" s="2" t="n"/>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Ambede</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Amberem</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9281,6 +11471,21 @@
       <c r="P187" s="2" t="n"/>
       <c r="Q187" s="2" t="n"/>
       <c r="R187" s="2" t="n"/>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Harmal</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Arambol</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9331,6 +11536,26 @@
       <c r="P188" s="2" t="n"/>
       <c r="Q188" s="2" t="n"/>
       <c r="R188" s="2" t="n"/>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Kamsarvarnem</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Cansarvornem</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Kasarvarne</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9446,6 +11671,26 @@
       <c r="P191" s="2" t="n"/>
       <c r="Q191" s="2" t="n"/>
       <c r="R191" s="2" t="n"/>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Chopde</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Chopdem</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Chopada</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9491,6 +11736,26 @@
       <c r="P192" s="2" t="n"/>
       <c r="Q192" s="2" t="n"/>
       <c r="R192" s="2" t="n"/>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Korgaon</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Corgao</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>Korgaon</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9541,6 +11806,31 @@
       <c r="P193" s="2" t="n"/>
       <c r="Q193" s="2" t="n"/>
       <c r="R193" s="2" t="n"/>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>धारगळ</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Dhargal</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Dargalim</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Dhargal</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9591,6 +11881,26 @@
       <c r="P194" s="2" t="n"/>
       <c r="Q194" s="2" t="n"/>
       <c r="R194" s="2" t="n"/>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Ibrampur</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Ibrampur</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Ibrampur</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9711,6 +12021,26 @@
       <c r="P196" s="2" t="n"/>
       <c r="Q196" s="2" t="n"/>
       <c r="R196" s="2" t="n"/>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>मोप</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Mop</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>Mopa</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9766,6 +12096,21 @@
       <c r="P197" s="2" t="n"/>
       <c r="Q197" s="2" t="n"/>
       <c r="R197" s="2" t="n"/>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Morji</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Morgim</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9861,6 +12206,21 @@
       <c r="P199" s="2" t="n"/>
       <c r="Q199" s="2" t="n"/>
       <c r="R199" s="2" t="n"/>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Palye</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Paliem</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9916,6 +12276,26 @@
       <c r="P200" s="2" t="n"/>
       <c r="Q200" s="2" t="n"/>
       <c r="R200" s="2" t="n"/>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Parshem</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Parcem</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>Parse</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9951,6 +12331,31 @@
       <c r="P201" s="2" t="n"/>
       <c r="Q201" s="2" t="n"/>
       <c r="R201" s="2" t="n"/>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>पेडणें</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Pedne</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Pernem</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>Perne</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10091,6 +12496,26 @@
       <c r="P204" s="2" t="n"/>
       <c r="Q204" s="2" t="n"/>
       <c r="R204" s="2" t="n"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Tamboshe</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Tamboxem</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Tambose</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -10136,6 +12561,31 @@
       <c r="P205" s="2" t="n"/>
       <c r="Q205" s="2" t="n"/>
       <c r="R205" s="2" t="n"/>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>तेरेखोल</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Terekhol</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Tiracol</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Terekhol</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -10181,6 +12631,26 @@
       <c r="P206" s="2" t="n"/>
       <c r="Q206" s="2" t="n"/>
       <c r="R206" s="2" t="n"/>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Torshe</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Torxem</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Torse</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10226,6 +12696,21 @@
       <c r="P207" s="2" t="n"/>
       <c r="Q207" s="2" t="n"/>
       <c r="R207" s="2" t="n"/>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Tuye</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Tuem</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -10316,6 +12801,26 @@
       <c r="P209" s="2" t="n"/>
       <c r="Q209" s="2" t="n"/>
       <c r="R209" s="2" t="n"/>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Varkhand</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Varconda</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>Varkhand</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10366,6 +12871,21 @@
       <c r="P210" s="2" t="n"/>
       <c r="Q210" s="2" t="n"/>
       <c r="R210" s="2" t="n"/>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Virnora</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Vinoda</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10411,6 +12931,26 @@
       <c r="P211" s="2" t="n"/>
       <c r="Q211" s="2" t="n"/>
       <c r="R211" s="2" t="n"/>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Advai</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Advoi</t>
+        </is>
+      </c>
+      <c r="X211" t="inlineStr">
+        <is>
+          <t>Advai</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10461,6 +13001,26 @@
       <c r="P212" s="2" t="n"/>
       <c r="Q212" s="2" t="n"/>
       <c r="R212" s="2" t="n"/>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Ambede</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Ambedem</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Ambede</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10511,6 +13071,31 @@
       <c r="P213" s="2" t="n"/>
       <c r="Q213" s="2" t="n"/>
       <c r="R213" s="2" t="n"/>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>आंबेली</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Ambel</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Ambeli</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr">
+        <is>
+          <t>Ambeli</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -10591,6 +13176,26 @@
       <c r="P215" s="2" t="n"/>
       <c r="Q215" s="2" t="n"/>
       <c r="R215" s="2" t="n"/>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>असोळयें</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Asolye</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Ansolem</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -10641,6 +13246,21 @@
       <c r="P216" s="2" t="n"/>
       <c r="Q216" s="2" t="n"/>
       <c r="R216" s="2" t="n"/>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Asode</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Assodem</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -10686,6 +13306,16 @@
       <c r="P217" s="2" t="n"/>
       <c r="Q217" s="2" t="n"/>
       <c r="R217" s="2" t="n"/>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Bhironde</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10736,6 +13366,26 @@
       <c r="P218" s="2" t="n"/>
       <c r="Q218" s="2" t="n"/>
       <c r="R218" s="2" t="n"/>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Bombede</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Bombedem</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Bombede</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10881,6 +13531,16 @@
       <c r="P221" s="2" t="n"/>
       <c r="Q221" s="2" t="n"/>
       <c r="R221" s="2" t="n"/>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Carambolim-Buzruco</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10971,6 +13631,21 @@
       <c r="P223" s="2" t="n"/>
       <c r="Q223" s="2" t="n"/>
       <c r="R223" s="2" t="n"/>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Charavane</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Choraundem</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -11016,6 +13691,31 @@
       <c r="P224" s="2" t="n"/>
       <c r="Q224" s="2" t="n"/>
       <c r="R224" s="2" t="n"/>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>कोदाळ</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Kodal</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Codal</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr">
+        <is>
+          <t>Kodal</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -11061,6 +13761,21 @@
       <c r="P225" s="2" t="n"/>
       <c r="Q225" s="2" t="n"/>
       <c r="R225" s="2" t="n"/>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Khodye</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Codiem</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -11106,6 +13821,21 @@
       <c r="P226" s="2" t="n"/>
       <c r="Q226" s="2" t="n"/>
       <c r="R226" s="2" t="n"/>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Khadki</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Codqui</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -11191,6 +13921,21 @@
       <c r="P228" s="2" t="n"/>
       <c r="Q228" s="2" t="n"/>
       <c r="R228" s="2" t="n"/>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Komparde</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Compordem</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -11226,6 +13971,21 @@
       <c r="P229" s="2" t="n"/>
       <c r="Q229" s="2" t="n"/>
       <c r="R229" s="2" t="n"/>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Kankire</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Conquirem</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -11276,6 +14036,21 @@
       <c r="P230" s="2" t="n"/>
       <c r="Q230" s="2" t="n"/>
       <c r="R230" s="2" t="n"/>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Khotode</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Cotorem</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -11311,6 +14086,21 @@
       <c r="P231" s="2" t="n"/>
       <c r="Q231" s="2" t="n"/>
       <c r="R231" s="2" t="n"/>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Kudshe</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Cudcem</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -11361,6 +14151,21 @@
       <c r="P232" s="2" t="n"/>
       <c r="Q232" s="2" t="n"/>
       <c r="R232" s="2" t="n"/>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Kumarkhand</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Cumarconda</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -11396,6 +14201,21 @@
       <c r="P233" s="2" t="n"/>
       <c r="Q233" s="2" t="n"/>
       <c r="R233" s="2" t="n"/>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Dabe</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Dabem</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -11446,6 +14266,21 @@
       <c r="P234" s="2" t="n"/>
       <c r="Q234" s="2" t="n"/>
       <c r="R234" s="2" t="n"/>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Dhamshe</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Damocem</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -11496,6 +14331,26 @@
       <c r="P235" s="2" t="n"/>
       <c r="Q235" s="2" t="n"/>
       <c r="R235" s="2" t="n"/>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>धावे</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Dhave</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Davem</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -11546,6 +14401,26 @@
       <c r="P236" s="2" t="n"/>
       <c r="Q236" s="2" t="n"/>
       <c r="R236" s="2" t="n"/>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>देरोडे</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Derode</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Derodem</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -11646,6 +14521,16 @@
       <c r="P238" s="2" t="n"/>
       <c r="Q238" s="2" t="n"/>
       <c r="R238" s="2" t="n"/>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Edorem</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -11691,6 +14576,26 @@
       <c r="P239" s="2" t="n"/>
       <c r="Q239" s="2" t="n"/>
       <c r="R239" s="2" t="n"/>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>गोळावली</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Golavli</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Golauli</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -11741,6 +14646,21 @@
       <c r="P240" s="2" t="n"/>
       <c r="Q240" s="2" t="n"/>
       <c r="R240" s="2" t="n"/>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Ghonteli</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Gonteli</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -11791,6 +14711,26 @@
       <c r="P241" s="2" t="n"/>
       <c r="Q241" s="2" t="n"/>
       <c r="R241" s="2" t="n"/>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>गोवणें</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Govane</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Govanem</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -11841,6 +14781,16 @@
       <c r="P242" s="2" t="n"/>
       <c r="Q242" s="2" t="n"/>
       <c r="R242" s="2" t="n"/>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Guleli</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -11886,6 +14836,16 @@
       <c r="P243" s="2" t="n"/>
       <c r="Q243" s="2" t="n"/>
       <c r="R243" s="2" t="n"/>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Gululem</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -12031,6 +14991,26 @@
       <c r="P246" s="2" t="n"/>
       <c r="Q246" s="2" t="n"/>
       <c r="R246" s="2" t="n"/>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>माळोली</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Maloli</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Maloli</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -12076,6 +15056,26 @@
       <c r="P247" s="2" t="n"/>
       <c r="Q247" s="2" t="n"/>
       <c r="R247" s="2" t="n"/>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>मळपण</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Malpan</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Malpona</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -12111,6 +15111,21 @@
       <c r="P248" s="2" t="n"/>
       <c r="Q248" s="2" t="n"/>
       <c r="R248" s="2" t="n"/>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Masorde</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Massordem</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -12206,6 +15221,21 @@
       <c r="P250" s="2" t="n"/>
       <c r="Q250" s="2" t="n"/>
       <c r="R250" s="2" t="n"/>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Melavali</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Melauli</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -12256,6 +15286,21 @@
       <c r="P251" s="2" t="n"/>
       <c r="Q251" s="2" t="n"/>
       <c r="R251" s="2" t="n"/>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Morle</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Morlem</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -12291,6 +15336,21 @@
       <c r="P252" s="2" t="n"/>
       <c r="Q252" s="2" t="n"/>
       <c r="R252" s="2" t="n"/>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Nagargaon</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Nagargao</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -12386,6 +15446,21 @@
       <c r="P254" s="2" t="n"/>
       <c r="Q254" s="2" t="n"/>
       <c r="R254" s="2" t="n"/>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Naneli</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Naneli</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -12431,6 +15506,26 @@
       <c r="P255" s="2" t="n"/>
       <c r="Q255" s="2" t="n"/>
       <c r="R255" s="2" t="n"/>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Nanode</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Nanorem</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>Nanode</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -12466,6 +15561,26 @@
       <c r="P256" s="2" t="n"/>
       <c r="Q256" s="2" t="n"/>
       <c r="R256" s="2" t="n"/>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Nanus</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Nanus</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>Nanuz</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -12521,6 +15636,31 @@
       <c r="P257" s="2" t="n"/>
       <c r="Q257" s="2" t="n"/>
       <c r="R257" s="2" t="n"/>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>होंड</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Hond</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Onda</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>Honda</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -12566,6 +15706,26 @@
       <c r="P258" s="2" t="n"/>
       <c r="Q258" s="2" t="n"/>
       <c r="R258" s="2" t="n"/>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>पाडेली</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Padeli</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Padeli</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -12661,6 +15821,21 @@
       <c r="P260" s="2" t="n"/>
       <c r="Q260" s="2" t="n"/>
       <c r="R260" s="2" t="n"/>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Pendal</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Pendral</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -12756,6 +15931,21 @@
       <c r="P262" s="2" t="n"/>
       <c r="Q262" s="2" t="n"/>
       <c r="R262" s="2" t="n"/>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Podashe</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Podocem</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -12801,6 +15991,21 @@
       <c r="P263" s="2" t="n"/>
       <c r="Q263" s="2" t="n"/>
       <c r="R263" s="2" t="n"/>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Panashe</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Ponocem</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -12836,6 +16041,26 @@
       <c r="P264" s="2" t="n"/>
       <c r="Q264" s="2" t="n"/>
       <c r="R264" s="2" t="n"/>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Panasuli</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Ponsuli</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>Pansulen</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -12881,6 +16106,26 @@
       <c r="P265" s="2" t="n"/>
       <c r="Q265" s="2" t="n"/>
       <c r="R265" s="2" t="n"/>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Parye</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Poriem</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Pariye</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -12926,6 +16171,16 @@
       <c r="P266" s="2" t="n"/>
       <c r="Q266" s="2" t="n"/>
       <c r="R266" s="2" t="n"/>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Quelaudem</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -13061,6 +16316,26 @@
       <c r="P269" s="2" t="n"/>
       <c r="Q269" s="2" t="n"/>
       <c r="R269" s="2" t="n"/>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>रिवें</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Riye</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>Rivem</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -13106,6 +16381,26 @@
       <c r="P270" s="2" t="n"/>
       <c r="Q270" s="2" t="n"/>
       <c r="R270" s="2" t="n"/>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>सालय</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Salai</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Saleli</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -13151,6 +16446,21 @@
       <c r="P271" s="2" t="n"/>
       <c r="Q271" s="2" t="n"/>
       <c r="R271" s="2" t="n"/>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Sanvarshe</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Sanvorcem</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -13251,6 +16561,26 @@
       <c r="P273" s="2" t="n"/>
       <c r="Q273" s="2" t="n"/>
       <c r="R273" s="2" t="n"/>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>सातोडें</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Satode</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Satorem</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -13296,6 +16626,21 @@
       <c r="P274" s="2" t="n"/>
       <c r="Q274" s="2" t="n"/>
       <c r="R274" s="2" t="n"/>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Satre</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Satrem</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -13341,6 +16686,21 @@
       <c r="P275" s="2" t="n"/>
       <c r="Q275" s="2" t="n"/>
       <c r="R275" s="2" t="n"/>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Shingone</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Sigonem</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -13376,6 +16736,26 @@
       <c r="P276" s="2" t="n"/>
       <c r="Q276" s="2" t="n"/>
       <c r="R276" s="2" t="n"/>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>शिरांगुळी</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Suranguli</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Siranguli</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -13426,6 +16806,21 @@
       <c r="P277" s="2" t="n"/>
       <c r="Q277" s="2" t="n"/>
       <c r="R277" s="2" t="n"/>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Shiroli</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Siroli</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -13516,6 +16911,26 @@
       <c r="P279" s="2" t="n"/>
       <c r="Q279" s="2" t="n"/>
       <c r="R279" s="2" t="n"/>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>सोनाळ</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Sonal</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Sonal</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -13561,6 +16976,21 @@
       <c r="P280" s="2" t="n"/>
       <c r="Q280" s="2" t="n"/>
       <c r="R280" s="2" t="n"/>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Sonshi</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Sonus-Vonvoliem</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -13656,6 +17086,21 @@
       <c r="P282" s="2" t="n"/>
       <c r="Q282" s="2" t="n"/>
       <c r="R282" s="2" t="n"/>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Uste</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>Ustem</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -13701,6 +17146,21 @@
       <c r="P283" s="2" t="n"/>
       <c r="Q283" s="2" t="n"/>
       <c r="R283" s="2" t="n"/>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Vaguriem</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>Vageri</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -13781,6 +17241,26 @@
       <c r="P285" s="2" t="n"/>
       <c r="Q285" s="2" t="n"/>
       <c r="R285" s="2" t="n"/>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Valpai</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Valpoi</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>Valpoy</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -13826,6 +17306,21 @@
       <c r="P286" s="2" t="n"/>
       <c r="Q286" s="2" t="n"/>
       <c r="R286" s="2" t="n"/>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Vante</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Vantem</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -14116,6 +17611,26 @@
       <c r="P293" s="2" t="n"/>
       <c r="Q293" s="2" t="n"/>
       <c r="R293" s="2" t="n"/>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>Ambadi</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>Ambarim</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>Ambari</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -14161,6 +17676,21 @@
       <c r="P294" s="2" t="n"/>
       <c r="Q294" s="2" t="n"/>
       <c r="R294" s="2" t="n"/>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>Adoshi</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>Azossim</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -14206,6 +17736,21 @@
       <c r="P295" s="2" t="n"/>
       <c r="Q295" s="2" t="n"/>
       <c r="R295" s="2" t="n"/>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>बायंगिणी</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>Baingini</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -14266,6 +17811,31 @@
       <c r="P296" s="2" t="n"/>
       <c r="Q296" s="2" t="n"/>
       <c r="R296" s="2" t="n"/>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>बांबोळी</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Bamboli</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>Bambolim</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>Bambolin</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -14301,6 +17871,26 @@
       <c r="P297" s="2" t="n"/>
       <c r="Q297" s="2" t="n"/>
       <c r="R297" s="2" t="n"/>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Bhati</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>Batim</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>Bhati</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -14401,6 +17991,26 @@
       <c r="P299" s="2" t="n"/>
       <c r="Q299" s="2" t="n"/>
       <c r="R299" s="2" t="n"/>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>कापांव</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>Kapao</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W299" t="inlineStr">
+        <is>
+          <t>Capao</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -14446,6 +18056,26 @@
       <c r="P300" s="2" t="n"/>
       <c r="Q300" s="2" t="n"/>
       <c r="R300" s="2" t="n"/>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>कारई</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>Karai</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>Caraim</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -14491,6 +18121,26 @@
       <c r="P301" s="2" t="n"/>
       <c r="Q301" s="2" t="n"/>
       <c r="R301" s="2" t="n"/>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>करंबळी</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>Karmali</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W301" t="inlineStr">
+        <is>
+          <t>Carambolim</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -14551,6 +18201,26 @@
       <c r="P302" s="2" t="n"/>
       <c r="Q302" s="2" t="n"/>
       <c r="R302" s="2" t="n"/>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>Chimbal</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W302" t="inlineStr">
+        <is>
+          <t>Chimbel</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>Chimbel</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -14586,9 +18256,24 @@
       <c r="P303" s="2" t="n"/>
       <c r="Q303" s="2" t="n"/>
       <c r="R303" s="2" t="n"/>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>Chodan</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
       <c r="V303" t="inlineStr">
         <is>
           <t>Choddnnem</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>Chorao</t>
         </is>
       </c>
     </row>
@@ -14651,6 +18336,26 @@
       <c r="P304" s="2" t="n"/>
       <c r="Q304" s="2" t="n"/>
       <c r="R304" s="2" t="n"/>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>Khorli</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W304" t="inlineStr">
+        <is>
+          <t>Corlim</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>Korlim</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -14691,6 +18396,21 @@
       <c r="P305" s="2" t="n"/>
       <c r="Q305" s="2" t="n"/>
       <c r="R305" s="2" t="n"/>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>कुजरा</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>Cujira</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -14751,6 +18471,26 @@
       <c r="P306" s="2" t="n"/>
       <c r="Q306" s="2" t="n"/>
       <c r="R306" s="2" t="n"/>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>Kumarzuve</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W306" t="inlineStr">
+        <is>
+          <t>Cumbarjua</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>Kumbharjuven</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -14796,6 +18536,26 @@
       <c r="P307" s="2" t="n"/>
       <c r="Q307" s="2" t="n"/>
       <c r="R307" s="2" t="n"/>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>Kudak</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>Curca</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Kurka</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -14831,6 +18591,21 @@
       <c r="P308" s="2" t="n"/>
       <c r="Q308" s="2" t="n"/>
       <c r="R308" s="2" t="n"/>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>दुर्गावाडी</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W308" t="inlineStr">
+        <is>
+          <t>Durgavado</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -14881,6 +18656,26 @@
       <c r="P309" s="2" t="n"/>
       <c r="Q309" s="2" t="n"/>
       <c r="R309" s="2" t="n"/>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>Yela</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Vela Goa</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -15016,9 +18811,29 @@
       <c r="P312" s="2" t="n"/>
       <c r="Q312" s="2" t="n"/>
       <c r="R312" s="2" t="n"/>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>Vodle Goe</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
       <c r="V312" t="inlineStr">
         <is>
           <t>Vhoddlem Goem</t>
+        </is>
+      </c>
+      <c r="W312" t="inlineStr">
+        <is>
+          <t>Goa-Velha</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>Vela Goa</t>
         </is>
       </c>
     </row>
@@ -15066,6 +18881,16 @@
       <c r="P313" s="2" t="n"/>
       <c r="Q313" s="2" t="n"/>
       <c r="R313" s="2" t="n"/>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>Goalim-Moula</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -15166,6 +18991,21 @@
       <c r="P315" s="2" t="n"/>
       <c r="Q315" s="2" t="n"/>
       <c r="R315" s="2" t="n"/>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>Juve</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>Jua</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -15211,6 +19051,26 @@
       <c r="P316" s="2" t="n"/>
       <c r="Q316" s="2" t="n"/>
       <c r="R316" s="2" t="n"/>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>मालार</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>Malar</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>Malar</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -15256,9 +19116,29 @@
       <c r="P317" s="2" t="n"/>
       <c r="Q317" s="2" t="n"/>
       <c r="R317" s="2" t="n"/>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>Mandur</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
       <c r="V317" t="inlineStr">
         <is>
           <t>Mandura</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>Mandur</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Mandur</t>
         </is>
       </c>
     </row>
@@ -15316,6 +19196,21 @@
       <c r="P318" s="2" t="n"/>
       <c r="Q318" s="2" t="n"/>
       <c r="R318" s="2" t="n"/>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>Mercuri</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>Mercurim</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -15456,6 +19351,26 @@
       <c r="P321" s="2" t="n"/>
       <c r="Q321" s="2" t="n"/>
       <c r="R321" s="2" t="n"/>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>Muddi</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>Murda</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>Murida</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -15636,6 +19551,26 @@
       <c r="P325" s="2" t="n"/>
       <c r="Q325" s="2" t="n"/>
       <c r="R325" s="2" t="n"/>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>Dhakte Nevre</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>Neura-o-Pequeno</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>Nevra</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -15671,6 +19606,26 @@
       <c r="P326" s="2" t="n"/>
       <c r="Q326" s="2" t="n"/>
       <c r="R326" s="2" t="n"/>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -15711,6 +19666,26 @@
       <c r="P327" s="2" t="n"/>
       <c r="Q327" s="2" t="n"/>
       <c r="R327" s="2" t="n"/>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>पानवेल</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>Panelim</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -15751,6 +19726,26 @@
       <c r="P328" s="2" t="n"/>
       <c r="Q328" s="2" t="n"/>
       <c r="R328" s="2" t="n"/>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>रेनावडें</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>Ranvadi</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>Renovadi</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -15796,6 +19791,26 @@
       <c r="P329" s="2" t="n"/>
       <c r="Q329" s="2" t="n"/>
       <c r="R329" s="2" t="n"/>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>Shirdon</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>Siridao</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>Siridanv</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -15886,6 +19901,26 @@
       <c r="P331" s="2" t="n"/>
       <c r="Q331" s="2" t="n"/>
       <c r="R331" s="2" t="n"/>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>Talgaon</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>Taleigao</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Talgaon</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -15936,6 +19971,31 @@
       <c r="P332" s="2" t="n"/>
       <c r="Q332" s="2" t="n"/>
       <c r="R332" s="2" t="n"/>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>आरोसी</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>Arosi</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>Arossim</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>Arosin</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -15981,6 +20041,26 @@
       <c r="P333" s="2" t="n"/>
       <c r="Q333" s="2" t="n"/>
       <c r="R333" s="2" t="n"/>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>Kansauli</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>Cansaulim</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>Kansavlim</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -16041,6 +20121,26 @@
       <c r="P334" s="2" t="n"/>
       <c r="Q334" s="2" t="n"/>
       <c r="R334" s="2" t="n"/>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>Chikhli</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>Chicalim</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>Chikli</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -16086,6 +20186,21 @@
       <c r="P335" s="2" t="n"/>
       <c r="Q335" s="2" t="n"/>
       <c r="R335" s="2" t="n"/>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>Chicolna</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>Chikolna</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -16146,6 +20261,26 @@
       <c r="P336" s="2" t="n"/>
       <c r="Q336" s="2" t="n"/>
       <c r="R336" s="2" t="n"/>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>Kutthal</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>Cortalim</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>Kortali</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -16181,6 +20316,21 @@
       <c r="P337" s="2" t="n"/>
       <c r="Q337" s="2" t="n"/>
       <c r="R337" s="2" t="n"/>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>Cuelim</t>
+        </is>
+      </c>
+      <c r="X337" t="inlineStr">
+        <is>
+          <t>Kuyelim</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -16241,6 +20391,26 @@
       <c r="P338" s="2" t="n"/>
       <c r="Q338" s="2" t="n"/>
       <c r="R338" s="2" t="n"/>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>दाबोळी</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>Dabolim</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>Dabolim</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -16291,6 +20461,16 @@
       <c r="P339" s="2" t="n"/>
       <c r="Q339" s="2" t="n"/>
       <c r="R339" s="2" t="n"/>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W339" t="inlineStr">
+        <is>
+          <t>Issorcim</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -16426,6 +20606,31 @@
       <c r="P342" s="2" t="n"/>
       <c r="Q342" s="2" t="n"/>
       <c r="R342" s="2" t="n"/>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>केळशी</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>Kelshi</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>Quelossim</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>Kelshi</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -16521,6 +20726,26 @@
       <c r="P344" s="2" t="n"/>
       <c r="Q344" s="2" t="n"/>
       <c r="R344" s="2" t="n"/>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>Sankval</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>Sancoale</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>Sankawali</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -16671,6 +20896,21 @@
       <c r="P348" s="2" t="n"/>
       <c r="Q348" s="2" t="n"/>
       <c r="R348" s="2" t="n"/>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>Velsaon</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>Velsao</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -16716,6 +20956,26 @@
       <c r="P349" s="2" t="n"/>
       <c r="Q349" s="2" t="n"/>
       <c r="R349" s="2" t="n"/>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>हडकोळण</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>Hadkalan</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W349" t="inlineStr">
+        <is>
+          <t>Adcolna</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -16771,6 +21031,26 @@
       <c r="P350" s="2" t="n"/>
       <c r="Q350" s="2" t="n"/>
       <c r="R350" s="2" t="n"/>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>Bandode</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>Bandora</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>Bendode</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -16816,6 +21096,31 @@
       <c r="P351" s="2" t="n"/>
       <c r="Q351" s="2" t="n"/>
       <c r="R351" s="2" t="n"/>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>बेतोडें</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>Betode</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>Betora</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>Betora</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -16866,6 +21171,21 @@
       <c r="P352" s="2" t="n"/>
       <c r="Q352" s="2" t="n"/>
       <c r="R352" s="2" t="n"/>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>बेतकी</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>Betqui</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -16961,6 +21281,26 @@
       <c r="P354" s="2" t="n"/>
       <c r="Q354" s="2" t="n"/>
       <c r="R354" s="2" t="n"/>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>बोरी</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>Bori</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>Borim</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -17061,6 +21401,21 @@
       <c r="P356" s="2" t="n"/>
       <c r="Q356" s="2" t="n"/>
       <c r="R356" s="2" t="n"/>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>Khandole</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W356" t="inlineStr">
+        <is>
+          <t>Candola</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -17111,6 +21466,31 @@
       <c r="P357" s="2" t="n"/>
       <c r="Q357" s="2" t="n"/>
       <c r="R357" s="2" t="n"/>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>कोडार</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>Kodar</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>Codar</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>Kodar</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -17161,6 +21541,26 @@
       <c r="P358" s="2" t="n"/>
       <c r="Q358" s="2" t="n"/>
       <c r="R358" s="2" t="n"/>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>Konshe</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>Conxem</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>Konsen</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -17206,6 +21606,16 @@
       <c r="P359" s="2" t="n"/>
       <c r="Q359" s="2" t="n"/>
       <c r="R359" s="2" t="n"/>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>Kunkalye</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -17251,6 +21661,26 @@
       <c r="P360" s="2" t="n"/>
       <c r="Q360" s="2" t="n"/>
       <c r="R360" s="2" t="n"/>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>कुंडय</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>Kundai</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>Cundaim</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -17291,6 +21721,26 @@
       <c r="P361" s="2" t="n"/>
       <c r="Q361" s="2" t="n"/>
       <c r="R361" s="2" t="n"/>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>Kutti</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>Curti</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Kurti</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -17381,6 +21831,21 @@
       <c r="P363" s="2" t="n"/>
       <c r="Q363" s="2" t="n"/>
       <c r="R363" s="2" t="n"/>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>Ganje</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>Gangem</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -17441,6 +21906,26 @@
       <c r="P364" s="2" t="n"/>
       <c r="Q364" s="2" t="n"/>
       <c r="R364" s="2" t="n"/>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>Madkai</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>Marcaim</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>Madkai</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -17526,6 +22011,21 @@
       <c r="P366" s="2" t="n"/>
       <c r="Q366" s="2" t="n"/>
       <c r="R366" s="2" t="n"/>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>Vargaon</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>Orgao</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -17576,6 +22076,31 @@
       <c r="P367" s="2" t="n"/>
       <c r="Q367" s="2" t="n"/>
       <c r="R367" s="2" t="n"/>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>पंचवाडी</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>Panchavadi</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>Ponchavadi</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>Panchvadi</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -17611,6 +22136,26 @@
       <c r="P368" s="2" t="n"/>
       <c r="Q368" s="2" t="n"/>
       <c r="R368" s="2" t="n"/>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>Phonde</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>Ponda</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Ponda</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -17671,6 +22216,31 @@
       <c r="P369" s="2" t="n"/>
       <c r="Q369" s="2" t="n"/>
       <c r="R369" s="2" t="n"/>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>प्रियोळ</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>Priyol</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>Priol</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>Priol</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -17751,6 +22321,31 @@
       <c r="P371" s="2" t="n"/>
       <c r="Q371" s="2" t="n"/>
       <c r="R371" s="2" t="n"/>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>कवळें</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>Kavle</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>Queula</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>Kevlan</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -17806,6 +22401,21 @@
       <c r="P372" s="2" t="n"/>
       <c r="Q372" s="2" t="n"/>
       <c r="R372" s="2" t="n"/>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>Savai Vere</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Sawae Verem</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -17951,6 +22561,26 @@
       <c r="P375" s="2" t="n"/>
       <c r="Q375" s="2" t="n"/>
       <c r="R375" s="2" t="n"/>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>तिवरे</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>Tivre</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>Tivrem</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -18006,6 +22636,31 @@
       <c r="P376" s="2" t="n"/>
       <c r="Q376" s="2" t="n"/>
       <c r="R376" s="2" t="n"/>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>उसगांव</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>Usgaon</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>Usgao</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>Usgaon</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -18051,6 +22706,26 @@
       <c r="P377" s="2" t="n"/>
       <c r="Q377" s="2" t="n"/>
       <c r="R377" s="2" t="n"/>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>वाडी</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>Vadi</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>Vadi</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -18096,6 +22771,21 @@
       <c r="P378" s="2" t="n"/>
       <c r="Q378" s="2" t="n"/>
       <c r="R378" s="2" t="n"/>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>Vagurme</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>Vagurbem</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -18141,6 +22831,26 @@
       <c r="P379" s="2" t="n"/>
       <c r="Q379" s="2" t="n"/>
       <c r="R379" s="2" t="n"/>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>Velinga</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>Velinga</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>Veling</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -18191,6 +22901,16 @@
       <c r="P380" s="2" t="n"/>
       <c r="Q380" s="2" t="n"/>
       <c r="R380" s="2" t="n"/>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>Valvai</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -18236,6 +22956,21 @@
       <c r="P381" s="2" t="n"/>
       <c r="Q381" s="2" t="n"/>
       <c r="R381" s="2" t="n"/>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>Adsuli</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>Adsulim</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -18271,6 +23006,16 @@
       <c r="P382" s="2" t="n"/>
       <c r="Q382" s="2" t="n"/>
       <c r="R382" s="2" t="n"/>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>Ambelim</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -18371,6 +23116,31 @@
       <c r="P384" s="2" t="n"/>
       <c r="Q384" s="2" t="n"/>
       <c r="R384" s="2" t="n"/>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>असोळणें</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>Asolne</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>Assolna</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>Assolna</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -18431,9 +23201,29 @@
       <c r="P385" s="2" t="n"/>
       <c r="Q385" s="2" t="n"/>
       <c r="R385" s="2" t="n"/>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>बाणावली</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
       <c r="V385" t="inlineStr">
         <is>
           <t>Banavalli</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>Benaulim</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>Benavli</t>
         </is>
       </c>
     </row>
@@ -18486,9 +23276,29 @@
       <c r="P386" s="2" t="n"/>
       <c r="Q386" s="2" t="n"/>
       <c r="R386" s="2" t="n"/>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>बेताळभाटी</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>Betalbhati</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
       <c r="V386" t="inlineStr">
         <is>
           <t>Betpatte</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>Betalbatim</t>
         </is>
       </c>
     </row>
@@ -18536,6 +23346,21 @@
       <c r="P387" s="2" t="n"/>
       <c r="Q387" s="2" t="n"/>
       <c r="R387" s="2" t="n"/>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>Kalat</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>Calata</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -18681,6 +23506,26 @@
       <c r="P390" s="2" t="n"/>
       <c r="Q390" s="2" t="n"/>
       <c r="R390" s="2" t="n"/>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>Karmane</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr">
+        <is>
+          <t>Carmona</t>
+        </is>
+      </c>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>Karmane</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -18726,6 +23571,31 @@
       <c r="P391" s="2" t="n"/>
       <c r="Q391" s="2" t="n"/>
       <c r="R391" s="2" t="n"/>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>केळशी</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>Kellshi</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>Cavelossim</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>Kalshi</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -18771,6 +23641,26 @@
       <c r="P392" s="2" t="n"/>
       <c r="Q392" s="2" t="n"/>
       <c r="R392" s="2" t="n"/>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>कावोरी</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>Kavori</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>Cavorim</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -18806,6 +23696,26 @@
       <c r="P393" s="2" t="n"/>
       <c r="Q393" s="2" t="n"/>
       <c r="R393" s="2" t="n"/>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>Chandar</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr">
+        <is>
+          <t>Chandor</t>
+        </is>
+      </c>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>Chandar</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -18861,9 +23771,29 @@
       <c r="P394" s="2" t="n"/>
       <c r="Q394" s="2" t="n"/>
       <c r="R394" s="2" t="n"/>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>Chinchone</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
       <c r="V394" t="inlineStr">
         <is>
           <t>Chinchone</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr">
+        <is>
+          <t>Chinchinim</t>
+        </is>
+      </c>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>Chinchinim</t>
         </is>
       </c>
     </row>
@@ -18911,6 +23841,26 @@
       <c r="P395" s="2" t="n"/>
       <c r="Q395" s="2" t="n"/>
       <c r="R395" s="2" t="n"/>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>Kolve</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>Colva</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>Kolva</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -18946,6 +23896,26 @@
       <c r="P396" s="2" t="n"/>
       <c r="Q396" s="2" t="n"/>
       <c r="R396" s="2" t="n"/>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>Kunkalli</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>Cuncolim</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>Kunkalli</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -19001,6 +23971,26 @@
       <c r="P397" s="2" t="n"/>
       <c r="Q397" s="2" t="n"/>
       <c r="R397" s="2" t="n"/>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>Kudtari</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr">
+        <is>
+          <t>Curtorim</t>
+        </is>
+      </c>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>Kurtorin</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -19061,6 +24051,21 @@
       <c r="P398" s="2" t="n"/>
       <c r="Q398" s="2" t="n"/>
       <c r="R398" s="2" t="n"/>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr">
+        <is>
+          <t>Davorlim</t>
+        </is>
+      </c>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>Daorlin</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -19106,6 +24111,16 @@
       <c r="P399" s="2" t="n"/>
       <c r="Q399" s="2" t="n"/>
       <c r="R399" s="2" t="n"/>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>Deussua</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -19156,6 +24171,26 @@
       <c r="P400" s="2" t="n"/>
       <c r="Q400" s="2" t="n"/>
       <c r="R400" s="2" t="n"/>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>दिकार्पाल</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>Dikarpal</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>Dicarpale</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -19206,6 +24241,26 @@
       <c r="P401" s="2" t="n"/>
       <c r="Q401" s="2" t="n"/>
       <c r="R401" s="2" t="n"/>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>Dharmapur</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>Dramapur</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>Dramapur</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -19251,6 +24306,21 @@
       <c r="P402" s="2" t="n"/>
       <c r="Q402" s="2" t="n"/>
       <c r="R402" s="2" t="n"/>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>Dhunkali</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>Duncolim</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -19391,6 +24461,16 @@
       <c r="P405" s="2" t="n"/>
       <c r="Q405" s="2" t="n"/>
       <c r="R405" s="2" t="n"/>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>Guirdolim</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -19436,6 +24516,26 @@
       <c r="P406" s="2" t="n"/>
       <c r="Q406" s="2" t="n"/>
       <c r="R406" s="2" t="n"/>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>लोटली</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>Lotli</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>Loutulim</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -19481,6 +24581,21 @@
       <c r="P407" s="2" t="n"/>
       <c r="Q407" s="2" t="n"/>
       <c r="R407" s="2" t="n"/>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>माखजन</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>Macasana</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -19526,6 +24641,31 @@
       <c r="P408" s="2" t="n"/>
       <c r="Q408" s="2" t="n"/>
       <c r="R408" s="2" t="n"/>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>माजोडें</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>Mazodde</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>Majorda</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>Majorda</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -19561,7 +24701,32 @@
       <c r="P409" s="2" t="n"/>
       <c r="Q409" s="2" t="n"/>
       <c r="R409" s="2" t="n"/>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>मडगांव</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>Madgaon</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
       <c r="V409" t="inlineStr">
+        <is>
+          <t>Madgaon</t>
+        </is>
+      </c>
+      <c r="W409" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="X409" t="inlineStr">
         <is>
           <t>Madgaon</t>
         </is>
@@ -19611,6 +24776,21 @@
       <c r="P410" s="2" t="n"/>
       <c r="Q410" s="2" t="n"/>
       <c r="R410" s="2" t="n"/>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>Mule</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W410" t="inlineStr">
+        <is>
+          <t>Mulem</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -19656,6 +24836,26 @@
       <c r="P411" s="2" t="n"/>
       <c r="Q411" s="2" t="n"/>
       <c r="R411" s="2" t="n"/>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>Nagve</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>Nagoa</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>Nagowa</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -19776,6 +24976,26 @@
       <c r="P413" s="2" t="n"/>
       <c r="Q413" s="2" t="n"/>
       <c r="R413" s="2" t="n"/>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>Nuve</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>Nuvem</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>Nuven</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -19821,6 +25041,26 @@
       <c r="P414" s="2" t="n"/>
       <c r="Q414" s="2" t="n"/>
       <c r="R414" s="2" t="n"/>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>ओडली</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>Odli</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>Orlim</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -19866,6 +25106,31 @@
       <c r="P415" s="2" t="n"/>
       <c r="Q415" s="2" t="n"/>
       <c r="R415" s="2" t="n"/>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>पारोडें</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>Padde</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W415" t="inlineStr">
+        <is>
+          <t>Paroda</t>
+        </is>
+      </c>
+      <c r="X415" t="inlineStr">
+        <is>
+          <t>Paroda</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -19901,6 +25166,31 @@
       <c r="P416" s="2" t="n"/>
       <c r="Q416" s="2" t="n"/>
       <c r="R416" s="2" t="n"/>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>रायतूर</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>Raitur</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>Rachol</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Rashol(Raitur)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -19961,6 +25251,26 @@
       <c r="P417" s="2" t="n"/>
       <c r="Q417" s="2" t="n"/>
       <c r="R417" s="2" t="n"/>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>Raya</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>Raia</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>Ray</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -20066,6 +25376,21 @@
       <c r="P419" s="2" t="n"/>
       <c r="Q419" s="2" t="n"/>
       <c r="R419" s="2" t="n"/>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>Soldade</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>Sarzora</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -20101,6 +25426,26 @@
       <c r="P420" s="2" t="n"/>
       <c r="Q420" s="2" t="n"/>
       <c r="R420" s="2" t="n"/>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>शिरावली</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>Suravali</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>Seraulim</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -20181,6 +25526,31 @@
       <c r="P422" s="2" t="n"/>
       <c r="Q422" s="2" t="n"/>
       <c r="R422" s="2" t="n"/>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>शिर्ली</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>Shilli</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>Sirlim</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>Sirli</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -20266,6 +25636,21 @@
       <c r="P424" s="2" t="n"/>
       <c r="Q424" s="2" t="n"/>
       <c r="R424" s="2" t="n"/>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>Talvade</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>Talvorda</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -20311,6 +25696,26 @@
       <c r="P425" s="2" t="n"/>
       <c r="Q425" s="2" t="n"/>
       <c r="R425" s="2" t="n"/>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>Utadde</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>Utorda</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>Utarda</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -20361,6 +25766,26 @@
       <c r="P426" s="2" t="n"/>
       <c r="Q426" s="2" t="n"/>
       <c r="R426" s="2" t="n"/>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>Vaneli</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>Vanelim</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>Vanelin</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -20416,6 +25841,26 @@
       <c r="P427" s="2" t="n"/>
       <c r="Q427" s="2" t="n"/>
       <c r="R427" s="2" t="n"/>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>Varke</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>Varca</t>
+        </is>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>Varka</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -20501,6 +25946,21 @@
       <c r="P429" s="2" t="n"/>
       <c r="Q429" s="2" t="n"/>
       <c r="R429" s="2" t="n"/>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>Velim</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>Vellim</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -20551,6 +26011,26 @@
       <c r="P430" s="2" t="n"/>
       <c r="Q430" s="2" t="n"/>
       <c r="R430" s="2" t="n"/>
+      <c r="T430" t="inlineStr">
+        <is>
+          <t>Verne</t>
+        </is>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>Verna</t>
+        </is>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>Varna</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:X430"/>
